--- a/data/trans_dic/P56$familiar-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P56$familiar-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 93,12</t>
+          <t>0,0; 76,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,59; 86,0</t>
+          <t>14,22; 85,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,58; 59,6</t>
+          <t>8,38; 66,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,13; 96,78</t>
+          <t>20,22; 96,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,26; 65,88</t>
+          <t>23,25; 65,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,55; 82,15</t>
+          <t>30,44; 81,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>48,4; 91,42</t>
+          <t>45,8; 91,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,77</t>
+          <t>0,0; 63,48</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29,11; 65,95</t>
+          <t>28,87; 66,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30,51; 68,03</t>
+          <t>30,14; 67,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>48,0; 87,53</t>
+          <t>49,32; 87,34</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,6</t>
+          <t>0,0; 70,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,23</t>
+          <t>0,0; 45,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,27; 71,87</t>
+          <t>21,36; 72,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,85; 49,04</t>
+          <t>5,87; 47,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,89; 24,98</t>
+          <t>2,95; 25,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,35; 67,79</t>
+          <t>13,56; 64,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>50,95; 72,51</t>
+          <t>51,32; 73,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,46; 43,71</t>
+          <t>8,57; 41,94</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,13; 22,07</t>
+          <t>4,16; 22,54</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,99; 53,9</t>
+          <t>10,13; 51,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>47,01; 69,02</t>
+          <t>47,79; 69,41</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,59</t>
+          <t>0,0; 50,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38,81; 73,32</t>
+          <t>38,25; 74,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,53</t>
+          <t>0,0; 39,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,0; 55,64</t>
+          <t>11,38; 60,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,97</t>
+          <t>0,0; 55,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>37,7; 62,28</t>
+          <t>37,55; 62,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,32</t>
+          <t>0,0; 35,85</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,5; 46,04</t>
+          <t>11,34; 44,64</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,59</t>
+          <t>0,0; 40,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>43,43; 62,46</t>
+          <t>42,0; 62,25</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,5; 75,61</t>
+          <t>11,31; 75,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,98</t>
+          <t>0,0; 36,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,57; 75,2</t>
+          <t>22,51; 74,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,65</t>
+          <t>0,0; 42,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,75; 71,87</t>
+          <t>28,97; 71,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,74; 50,58</t>
+          <t>5,37; 50,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>54,77; 79,86</t>
+          <t>53,77; 78,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,77</t>
+          <t>0,0; 33,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31,66; 67,98</t>
+          <t>28,24; 65,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 39,06</t>
+          <t>6,17; 39,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,71; 73,9</t>
+          <t>49,77; 74,25</t>
         </is>
       </c>
     </row>
@@ -1287,52 +1287,52 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,06; 66,33</t>
+          <t>18,84; 65,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,87</t>
+          <t>0,0; 64,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,6; 47,55</t>
+          <t>5,2; 42,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,07</t>
+          <t>0,0; 39,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>42,68; 69,7</t>
+          <t>40,37; 70,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,88; 54,87</t>
+          <t>6,37; 55,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,31; 48,96</t>
+          <t>11,97; 49,1</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,84</t>
+          <t>0,0; 43,03</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,63; 63,51</t>
+          <t>38,78; 63,94</t>
         </is>
       </c>
     </row>
@@ -1422,57 +1422,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,13</t>
+          <t>0,0; 60,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,51</t>
+          <t>0,0; 48,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>37,58; 67,89</t>
+          <t>37,16; 68,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,97</t>
+          <t>0,0; 58,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,43; 52,29</t>
+          <t>10,56; 52,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,8</t>
+          <t>0,0; 34,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>41,3; 61,82</t>
+          <t>40,75; 61,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,13; 51,91</t>
+          <t>5,88; 51,03</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,56; 44,67</t>
+          <t>13,48; 45,15</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,11; 30,02</t>
+          <t>3,54; 30,01</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>43,84; 60,64</t>
+          <t>43,23; 61,4</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,44</t>
+          <t>0,0; 65,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,26</t>
+          <t>0,0; 39,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,36; 39,53</t>
+          <t>4,44; 41,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23,95; 72,14</t>
+          <t>23,94; 71,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,37 +1582,37 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,37; 48,28</t>
+          <t>16,83; 49,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,67; 42,29</t>
+          <t>13,77; 42,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35,58; 58,39</t>
+          <t>34,99; 59,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,6</t>
+          <t>0,0; 52,68</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13,65; 38,73</t>
+          <t>13,3; 39,46</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13,13; 35,5</t>
+          <t>13,58; 36,35</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35,08; 56,34</t>
+          <t>36,03; 57,44</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,23; 44,99</t>
+          <t>8,82; 47,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,37; 85,98</t>
+          <t>9,13; 73,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,65; 63,5</t>
+          <t>8,06; 65,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33,16; 67,26</t>
+          <t>31,5; 65,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,81; 39,77</t>
+          <t>7,99; 40,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,37; 46,39</t>
+          <t>11,62; 44,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,66; 45,4</t>
+          <t>5,82; 48,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>47,76; 67,45</t>
+          <t>47,62; 67,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,18; 35,19</t>
+          <t>12,5; 36,62</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13,61; 45,13</t>
+          <t>14,78; 45,8</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9,86; 42,32</t>
+          <t>10,68; 44,49</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>47,77; 63,65</t>
+          <t>47,68; 63,92</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11,14; 32,15</t>
+          <t>10,28; 33,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,3; 37,43</t>
+          <t>16,04; 38,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,78; 26,46</t>
+          <t>9,76; 25,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>42,17; 57,74</t>
+          <t>42,71; 57,66</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,23; 27,09</t>
+          <t>10,87; 28,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,79; 37,03</t>
+          <t>22,83; 36,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,0; 33,24</t>
+          <t>18,22; 32,66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>51,84; 60,66</t>
+          <t>51,73; 60,64</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13,33; 26,2</t>
+          <t>12,54; 26,35</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23,59; 34,69</t>
+          <t>23,71; 34,3</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17,99; 29,64</t>
+          <t>17,63; 28,86</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>50,26; 57,99</t>
+          <t>50,47; 57,9</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3278</t>
+          <t>0; 2706</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1029; 6064</t>
+          <t>1002; 6056</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>852; 5920</t>
+          <t>832; 6635</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1013; 4868</t>
+          <t>1017; 4867</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1366</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5153; 13990</t>
+          <t>4938; 13899</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6171; 15107</t>
+          <t>5597; 15076</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3982; 7520</t>
+          <t>3767; 7487</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4012</t>
+          <t>0; 3758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8235; 18656</t>
+          <t>8168; 18855</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8640; 19268</t>
+          <t>8535; 19250</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6363; 11602</t>
+          <t>6537; 11578</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4857</t>
+          <t>0; 4859</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4711</t>
+          <t>0; 5272</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1449</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2596; 8769</t>
+          <t>2606; 8841</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>860; 7213</t>
+          <t>863; 6929</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1065; 9219</t>
+          <t>1090; 9503</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2557; 12080</t>
+          <t>2417; 11424</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21358; 30398</t>
+          <t>21514; 30820</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1826; 9436</t>
+          <t>1850; 9054</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2008; 10731</t>
+          <t>2024; 10961</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2562; 12559</t>
+          <t>2361; 11940</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25441; 37356</t>
+          <t>25863; 37566</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1303</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4781</t>
+          <t>0; 4697</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1397</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7107; 13427</t>
+          <t>7005; 13556</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5335</t>
+          <t>0; 4791</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3081; 10715</t>
+          <t>2192; 11614</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5815</t>
+          <t>0; 5996</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12634; 20872</t>
+          <t>12584; 20950</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5516</t>
+          <t>0; 5444</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3281; 13132</t>
+          <t>3234; 12732</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 5639</t>
+          <t>0; 6822</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22508; 32369</t>
+          <t>21764; 32262</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1146</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>999; 6566</t>
+          <t>982; 6586</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3500</t>
+          <t>0; 3625</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2187; 6976</t>
+          <t>2088; 6890</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4504</t>
+          <t>0; 4615</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6455; 16139</t>
+          <t>6505; 16109</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2180; 12606</t>
+          <t>1339; 12641</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10829; 15790</t>
+          <t>10632; 15530</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5460</t>
+          <t>0; 4440</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9859; 21168</t>
+          <t>8794; 20279</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2174; 13645</t>
+          <t>2154; 13700</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14150; 21465</t>
+          <t>14459; 21568</t>
         </is>
       </c>
     </row>
@@ -3051,52 +3051,52 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 616</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1430; 4975</t>
+          <t>1413; 4923</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5886</t>
+          <t>0; 5750</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1102; 9366</t>
+          <t>1025; 8370</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4733</t>
+          <t>0; 4735</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7078; 11559</t>
+          <t>6695; 11625</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>777; 7252</t>
+          <t>842; 7376</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3250; 12929</t>
+          <t>3160; 12964</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 5532</t>
+          <t>0; 5557</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9304; 15298</t>
+          <t>9342; 15400</t>
         </is>
       </c>
     </row>
@@ -3254,57 +3254,57 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6404</t>
+          <t>0; 6391</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5245</t>
+          <t>0; 5267</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6211; 11220</t>
+          <t>6141; 11349</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6114</t>
+          <t>0; 6190</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2107; 10560</t>
+          <t>2133; 10605</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 7692</t>
+          <t>0; 7658</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13116; 19635</t>
+          <t>12941; 19475</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>872; 7389</t>
+          <t>837; 7264</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4182; 13780</t>
+          <t>4158; 13927</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1025; 9882</t>
+          <t>1167; 9878</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21170; 29283</t>
+          <t>20875; 29646</t>
         </is>
       </c>
     </row>
@@ -3457,22 +3457,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3446</t>
+          <t>0; 3381</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 6106</t>
+          <t>0; 6083</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>869; 7886</t>
+          <t>885; 8197</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2972; 8951</t>
+          <t>2971; 8834</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3482,37 +3482,37 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5800; 17105</t>
+          <t>5961; 17368</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5863; 18141</t>
+          <t>5908; 18321</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>14919; 24483</t>
+          <t>14671; 24795</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4899</t>
+          <t>0; 4815</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6960; 19744</t>
+          <t>6781; 20117</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8253; 22314</t>
+          <t>8536; 22846</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>19063; 30612</t>
+          <t>19579; 31209</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1773; 8643</t>
+          <t>1694; 9132</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>833; 7640</t>
+          <t>811; 6487</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>788; 5781</t>
+          <t>734; 5957</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6897; 13992</t>
+          <t>6553; 13650</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2337; 11905</t>
+          <t>2392; 12228</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3420; 13947</t>
+          <t>3494; 13479</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1289; 10333</t>
+          <t>1324; 11114</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>27385; 38674</t>
+          <t>27301; 38632</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5492; 17295</t>
+          <t>6144; 17999</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5301; 17578</t>
+          <t>5758; 17837</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3143; 13487</t>
+          <t>3404; 14178</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>37324; 49733</t>
+          <t>37258; 49946</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>5379; 15524</t>
+          <t>4961; 16299</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>12799; 29383</t>
+          <t>12593; 29885</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7052; 19077</t>
+          <t>7036; 18674</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>43036; 58931</t>
+          <t>43587; 58844</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>10506; 25341</t>
+          <t>10165; 26329</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>48827; 76005</t>
+          <t>46863; 74566</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32633; 57110</t>
+          <t>31293; 56105</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>130128; 152263</t>
+          <t>129858; 152218</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>18898; 37160</t>
+          <t>17788; 37377</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>66930; 98422</t>
+          <t>67265; 97332</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>43864; 72276</t>
+          <t>42987; 70377</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>177458; 204769</t>
+          <t>178211; 204443</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$familiar-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P56$familiar-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>66,73%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,87</t>
+          <t>0,0; 90,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,22; 85,89</t>
+          <t>14,08; 85,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,38; 66,81</t>
+          <t>8,53; 59,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,22; 96,75</t>
+          <t>17,38; 87,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,25; 65,45</t>
+          <t>24,64; 65,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,44; 81,98</t>
+          <t>28,99; 79,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>45,8; 91,01</t>
+          <t>45,76; 89,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,48</t>
+          <t>0,0; 67,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,87; 66,66</t>
+          <t>29,12; 68,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30,14; 67,97</t>
+          <t>30,15; 67,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>49,32; 87,34</t>
+          <t>44,58; 83,78</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>57,87%</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,62</t>
+          <t>0,0; 70,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,02</t>
+          <t>0,0; 44,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,47 +872,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,36; 72,46</t>
+          <t>18,27; 71,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,87; 47,11</t>
+          <t>5,87; 41,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,95; 25,75</t>
+          <t>2,91; 27,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,56; 64,11</t>
+          <t>14,1; 67,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>51,32; 73,52</t>
+          <t>50,27; 73,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,57; 41,94</t>
+          <t>8,29; 44,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,16; 22,54</t>
+          <t>4,24; 24,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,13; 51,24</t>
+          <t>10,91; 52,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>47,79; 69,41</t>
+          <t>47,1; 68,73</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>51,88%</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,68</t>
+          <t>0,0; 48,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38,25; 74,02</t>
+          <t>40,11; 75,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,09</t>
+          <t>0,0; 42,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,38; 60,31</t>
+          <t>11,38; 60,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,65</t>
+          <t>0,0; 56,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>37,55; 62,52</t>
+          <t>37,63; 61,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,85</t>
+          <t>0,0; 33,9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,34; 44,64</t>
+          <t>10,88; 46,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,64</t>
+          <t>0,0; 41,94</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>42,0; 62,25</t>
+          <t>41,07; 60,74</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,4%</t>
         </is>
       </c>
     </row>
@@ -1142,57 +1142,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,31; 75,84</t>
+          <t>11,3; 76,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,23</t>
+          <t>0,0; 34,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,51; 74,28</t>
+          <t>23,28; 75,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,68</t>
+          <t>0,0; 41,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,97; 71,74</t>
+          <t>32,17; 71,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,37; 50,72</t>
+          <t>5,04; 51,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>53,77; 78,54</t>
+          <t>53,91; 80,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,15</t>
+          <t>0,0; 41,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,24; 65,12</t>
+          <t>27,96; 65,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,17; 39,22</t>
+          <t>6,23; 37,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49,77; 74,25</t>
+          <t>49,08; 74,2</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>51,45%</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,35; 83,47</t>
+          <t>15,3; 83,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,47 +1292,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,84; 65,63</t>
+          <t>18,18; 65,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,35</t>
+          <t>0,0; 64,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 42,49</t>
+          <t>5,53; 43,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,09</t>
+          <t>0,0; 39,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>40,37; 70,1</t>
+          <t>42,56; 71,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,37; 55,81</t>
+          <t>6,34; 59,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,97; 49,1</t>
+          <t>12,03; 48,54</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,03</t>
+          <t>0,0; 36,67</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,78; 63,94</t>
+          <t>38,37; 64,52</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,83%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,92</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,01</t>
+          <t>0,0; 50,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,71</t>
+          <t>0,0; 51,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>37,16; 68,67</t>
+          <t>37,45; 68,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,69</t>
+          <t>0,0; 58,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,56; 52,51</t>
+          <t>15,06; 57,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,65</t>
+          <t>0,0; 37,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>40,75; 61,32</t>
+          <t>40,31; 61,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,88; 51,03</t>
+          <t>5,87; 52,14</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,48; 45,15</t>
+          <t>13,29; 44,95</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,54; 30,01</t>
+          <t>3,66; 31,19</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>43,23; 61,4</t>
+          <t>42,64; 61,01</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>45,17%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,18</t>
+          <t>0,0; 66,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,12</t>
+          <t>0,0; 39,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,44; 41,09</t>
+          <t>4,45; 41,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23,94; 71,2</t>
+          <t>20,29; 70,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,61</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,83; 49,02</t>
+          <t>16,65; 48,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,77; 42,71</t>
+          <t>13,09; 41,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>34,99; 59,14</t>
+          <t>34,35; 56,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,68</t>
+          <t>0,0; 59,38</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13,3; 39,46</t>
+          <t>14,7; 40,86</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13,58; 36,35</t>
+          <t>13,21; 35,8</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36,03; 57,44</t>
+          <t>35,76; 55,37</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,36%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,82; 47,53</t>
+          <t>8,84; 44,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,13; 73,01</t>
+          <t>9,84; 85,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,06; 65,44</t>
+          <t>8,74; 67,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31,5; 65,62</t>
+          <t>32,25; 64,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,99; 40,85</t>
+          <t>7,73; 39,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,62; 44,84</t>
+          <t>11,66; 45,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,82; 48,83</t>
+          <t>5,78; 46,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>47,62; 67,38</t>
+          <t>47,87; 66,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,5; 36,62</t>
+          <t>11,53; 36,83</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14,78; 45,8</t>
+          <t>14,7; 45,37</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,68; 44,49</t>
+          <t>10,41; 43,7</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>47,68; 63,92</t>
+          <t>46,21; 64,3</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>53,76%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,28; 33,76</t>
+          <t>11,73; 33,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,04; 38,07</t>
+          <t>17,48; 38,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,76; 25,9</t>
+          <t>9,72; 26,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>42,71; 57,66</t>
+          <t>42,14; 57,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,87; 28,15</t>
+          <t>10,32; 27,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,83; 36,33</t>
+          <t>23,77; 36,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,22; 32,66</t>
+          <t>17,83; 32,5</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>51,73; 60,64</t>
+          <t>50,72; 60,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12,54; 26,35</t>
+          <t>12,78; 26,39</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23,71; 34,3</t>
+          <t>22,94; 34,07</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17,63; 28,86</t>
+          <t>17,31; 29,37</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>50,47; 57,9</t>
+          <t>49,81; 58,07</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>5974</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9418</t>
+          <t>9156</t>
         </is>
       </c>
     </row>
@@ -2209,22 +2209,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2706</t>
+          <t>0; 3171</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1002; 6056</t>
+          <t>993; 6062</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>832; 6635</t>
+          <t>847; 5927</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1017; 4867</t>
+          <t>915; 4625</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2234,37 +2234,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4938; 13899</t>
+          <t>5233; 13899</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5597; 15076</t>
+          <t>5330; 14625</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3767; 7487</t>
+          <t>3869; 7540</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3758</t>
+          <t>0; 3994</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8168; 18855</t>
+          <t>8238; 19418</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8535; 19250</t>
+          <t>8538; 19173</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6537; 11578</t>
+          <t>6116; 11494</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>5646</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26245</t>
+          <t>27798</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31571</t>
+          <t>33445</t>
         </is>
       </c>
     </row>
@@ -2417,12 +2417,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4859</t>
+          <t>0; 4838</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5272</t>
+          <t>0; 5221</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2432,47 +2432,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2606; 8841</t>
+          <t>2389; 9364</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>863; 6929</t>
+          <t>863; 6165</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1090; 9503</t>
+          <t>1076; 10187</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2417; 11424</t>
+          <t>2512; 12105</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21514; 30820</t>
+          <t>22477; 32706</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1850; 9054</t>
+          <t>1790; 9613</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2024; 10961</t>
+          <t>2062; 11675</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2361; 11940</t>
+          <t>2543; 12221</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25863; 37566</t>
+          <t>27223; 39723</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10443</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16746</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27188</t>
+          <t>26675</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4697</t>
+          <t>0; 4518</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2640,47 +2640,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7005; 13556</t>
+          <t>7169; 13522</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4791</t>
+          <t>0; 5267</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2192; 11614</t>
+          <t>2190; 11598</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5996</t>
+          <t>0; 6038</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12584; 20950</t>
+          <t>12622; 20559</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5444</t>
+          <t>0; 5148</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3234; 12732</t>
+          <t>3102; 13237</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 6822</t>
+          <t>0; 7040</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21764; 32262</t>
+          <t>21117; 31234</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4584</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13437</t>
+          <t>14165</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18021</t>
+          <t>18932</t>
         </is>
       </c>
     </row>
@@ -2838,57 +2838,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>982; 6586</t>
+          <t>981; 6601</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3625</t>
+          <t>0; 3453</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2088; 6890</t>
+          <t>2216; 7231</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4615</t>
+          <t>0; 4499</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6505; 16109</t>
+          <t>7223; 16123</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1339; 12641</t>
+          <t>1256; 12753</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10632; 15530</t>
+          <t>11225; 16782</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4440</t>
+          <t>0; 5557</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8794; 20279</t>
+          <t>8706; 20432</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2154; 13700</t>
+          <t>2177; 13173</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14459; 21568</t>
+          <t>14892; 22514</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2973</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12232</t>
+          <t>12808</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1029; 5598</t>
+          <t>1026; 5594</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3056,47 +3056,47 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1413; 4923</t>
+          <t>1396; 5015</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5750</t>
+          <t>0; 5736</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1025; 8370</t>
+          <t>1089; 8518</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>0; 4731</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>7327; 12387</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>838; 7798</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3178; 12817</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
           <t>0; 4735</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>6695; 11625</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>842; 7376</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>3160; 12964</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>0; 5557</t>
-        </is>
-      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9342; 15400</t>
+          <t>9551; 16061</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8774</t>
+          <t>8756</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>16694</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>25151</t>
+          <t>25450</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2688</t>
+          <t>0; 3687</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6391</t>
+          <t>0; 5366</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5267</t>
+          <t>0; 5611</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6141; 11349</t>
+          <t>6200; 11289</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6190</t>
+          <t>0; 6211</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2133; 10605</t>
+          <t>3042; 11581</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 7658</t>
+          <t>0; 8287</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12941; 19475</t>
+          <t>13122; 20073</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>837; 7264</t>
+          <t>836; 7422</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4158; 13927</t>
+          <t>4100; 13866</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1167; 9878</t>
+          <t>1204; 10268</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>20875; 29646</t>
+          <t>20938; 29958</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5575</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>19530</t>
+          <t>23307</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>25105</t>
+          <t>30056</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3381</t>
+          <t>0; 3434</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 6083</t>
+          <t>0; 6160</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>885; 8197</t>
+          <t>888; 8230</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2971; 8834</t>
+          <t>3024; 10568</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3068</t>
+          <t>0; 3953</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5961; 17368</t>
+          <t>5900; 17060</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5908; 18321</t>
+          <t>5616; 17705</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>14671; 24795</t>
+          <t>17733; 29036</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4815</t>
+          <t>0; 5428</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6781; 20117</t>
+          <t>7492; 20829</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8536; 22846</t>
+          <t>8305; 22500</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>19579; 31209</t>
+          <t>23797; 36845</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>11552</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>33093</t>
+          <t>38383</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>49935</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1694; 9132</t>
+          <t>1698; 8480</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>811; 6487</t>
+          <t>874; 7628</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>734; 5957</t>
+          <t>796; 6123</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6553; 13650</t>
+          <t>7642; 15261</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2392; 12228</t>
+          <t>2313; 11811</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3494; 13479</t>
+          <t>3504; 13649</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1324; 11114</t>
+          <t>1316; 10517</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>27301; 38632</t>
+          <t>31830; 44519</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6144; 17999</t>
+          <t>5665; 18101</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5758; 17837</t>
+          <t>5727; 17673</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3404; 14178</t>
+          <t>3316; 13924</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>37258; 49946</t>
+          <t>41682; 57997</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>51152</t>
+          <t>53787</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>140834</t>
+          <t>152671</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>191987</t>
+          <t>206457</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>4961; 16299</t>
+          <t>5663; 16148</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>12593; 29885</t>
+          <t>13724; 29980</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7036; 18674</t>
+          <t>7008; 19030</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>43587; 58844</t>
+          <t>45758; 62271</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>10165; 26329</t>
+          <t>9655; 25607</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>46863; 74566</t>
+          <t>48778; 74875</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31293; 56105</t>
+          <t>30624; 55836</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>129858; 152218</t>
+          <t>139710; 165284</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>17788; 37377</t>
+          <t>18120; 37429</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>67265; 97332</t>
+          <t>65087; 96671</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>42987; 70377</t>
+          <t>42208; 71623</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>178211; 204443</t>
+          <t>191274; 222974</t>
         </is>
       </c>
     </row>
